--- a/trace_compare_final_prefix_code_project/corrected_added_highlight_prefix_logic_output.xlsx
+++ b/trace_compare_final_prefix_code_project/corrected_added_highlight_prefix_logic_output.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MM_Repo\trace_compare_final_prefix_code_project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\New folder\MM_Automation\MottM_Automation\trace_compare_final_prefix_code_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B68E35F9-84BF-4B36-868D-EA679A926F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7090F070-5536-4E55-89FF-32E1FF6C1BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1_new" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="85">
   <si>
     <t>Part B: Technical Requirements</t>
   </si>
@@ -273,6 +273,9 @@
   </si>
   <si>
     <t>Project-SRS-0020</t>
+  </si>
+  <si>
+    <t>Project- PSTR-99999</t>
   </si>
 </sst>
 </file>
@@ -339,7 +342,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -427,11 +430,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -463,15 +479,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -778,12 +797,12 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:O30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="15" width="30.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="15" width="30.5703125" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -830,20 +849,20 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
       <c r="D2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
       <c r="G2" s="10"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
       <c r="J2" s="4" t="s">
         <v>11</v>
       </c>
@@ -863,16 +882,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:15" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
+    <row r="3" spans="1:15" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
       <c r="J3" s="4" t="s">
         <v>17</v>
       </c>
@@ -892,28 +911,28 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:15" s="1" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" s="1" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
       <c r="D4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="12" t="s">
         <v>24</v>
       </c>
       <c r="G4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="12" t="s">
         <v>27</v>
       </c>
       <c r="J4" s="4" t="s">
@@ -935,16 +954,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
+    <row r="5" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
       <c r="J5" s="4" t="s">
         <v>31</v>
       </c>
@@ -964,16 +983,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:15" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
+    <row r="6" spans="1:15" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
       <c r="J6" s="4" t="s">
         <v>34</v>
       </c>
@@ -993,20 +1012,20 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
+    <row r="7" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
       <c r="G7" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="12" t="s">
         <v>39</v>
       </c>
       <c r="J7" s="4" t="s">
@@ -1028,16 +1047,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+    <row r="8" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
       <c r="J8" s="4" t="s">
         <v>11</v>
       </c>
@@ -1057,16 +1076,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+    <row r="9" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
       <c r="J9" s="4" t="s">
         <v>43</v>
       </c>
@@ -1086,16 +1105,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:15" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+    <row r="10" spans="1:15" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
       <c r="J10" s="4" t="s">
         <v>34</v>
       </c>
@@ -1115,16 +1134,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
+    <row r="11" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
       <c r="J11" s="4" t="s">
         <v>46</v>
       </c>
@@ -1144,20 +1163,20 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
+    <row r="12" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
       <c r="G12" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="H12" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I12" s="12" t="s">
         <v>51</v>
       </c>
       <c r="J12" s="4" t="s">
@@ -1179,16 +1198,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
+    <row r="13" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
       <c r="J13" s="4" t="s">
         <v>55</v>
       </c>
@@ -1208,16 +1227,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
+    <row r="14" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
       <c r="J14" s="4" t="s">
         <v>58</v>
       </c>
@@ -1237,13 +1256,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
+    <row r="15" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
       <c r="G15" s="4"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
@@ -1266,20 +1285,20 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:15" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
+    <row r="16" spans="1:15" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
       <c r="D16" s="10"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
       <c r="G16" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="H16" s="13" t="s">
+      <c r="H16" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="I16" s="13" t="s">
+      <c r="I16" s="12" t="s">
         <v>63</v>
       </c>
       <c r="J16" s="4" t="s">
@@ -1301,16 +1320,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
+    <row r="17" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
       <c r="J17" s="4" t="s">
         <v>11</v>
       </c>
@@ -1330,16 +1349,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
+    <row r="18" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
       <c r="J18" s="4" t="s">
         <v>43</v>
       </c>
@@ -1359,16 +1378,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:15" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
+    <row r="19" spans="1:15" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
       <c r="J19" s="4" t="s">
         <v>67</v>
       </c>
@@ -1388,16 +1407,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
+    <row r="20" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
       <c r="J20" s="4" t="s">
         <v>58</v>
       </c>
@@ -1417,16 +1436,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:15" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
+    <row r="21" spans="1:15" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
       <c r="J21" s="4" t="s">
         <v>17</v>
       </c>
@@ -1446,16 +1465,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
+    <row r="22" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
       <c r="J22" s="4" t="s">
         <v>46</v>
       </c>
@@ -1475,16 +1494,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
+    <row r="23" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
       <c r="G23" s="10"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
       <c r="J23" s="4" t="s">
         <v>70</v>
       </c>
@@ -1504,16 +1523,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
+    <row r="24" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
       <c r="J24" s="4" t="s">
         <v>58</v>
       </c>
@@ -1533,7 +1552,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>73</v>
       </c>
@@ -1564,7 +1583,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>77</v>
       </c>
@@ -1583,7 +1602,7 @@
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
     </row>
-    <row r="27" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>78</v>
       </c>
@@ -1614,7 +1633,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:15" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>79</v>
       </c>
@@ -1633,7 +1652,7 @@
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>80</v>
       </c>
@@ -1654,7 +1673,7 @@
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>81</v>
       </c>
@@ -1675,18 +1694,10 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="G16:G22"/>
-    <mergeCell ref="F4:F15"/>
-    <mergeCell ref="E16:E24"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="E4:E15"/>
-    <mergeCell ref="G7:G11"/>
-    <mergeCell ref="D4:D15"/>
-    <mergeCell ref="F16:F24"/>
-    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H7:H11"/>
+    <mergeCell ref="D16:D24"/>
+    <mergeCell ref="H12:H14"/>
+    <mergeCell ref="H16:H22"/>
     <mergeCell ref="I4:I6"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="D2:D3"/>
@@ -1701,15 +1712,26 @@
     <mergeCell ref="I16:I22"/>
     <mergeCell ref="H23:H24"/>
     <mergeCell ref="I2:I3"/>
-    <mergeCell ref="A4:A24"/>
     <mergeCell ref="G23:G24"/>
     <mergeCell ref="B4:B24"/>
-    <mergeCell ref="H7:H11"/>
-    <mergeCell ref="D16:D24"/>
-    <mergeCell ref="H12:H14"/>
-    <mergeCell ref="H16:H22"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="G16:G22"/>
+    <mergeCell ref="F4:F15"/>
+    <mergeCell ref="E16:E24"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="E4:E15"/>
+    <mergeCell ref="G7:G11"/>
+    <mergeCell ref="D4:D15"/>
+    <mergeCell ref="F16:F24"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="A4:A24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Mott MacDonald Restricted</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1718,13 +1740,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:O48"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:O49"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="15" width="30.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="15" width="30.5703125" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1771,41 +1793,43 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:15" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+    </row>
+    <row r="3" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="10" t="s">
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E3" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F3" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-    </row>
-    <row r="3" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
       <c r="J3" s="4"/>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
@@ -1813,16 +1837,16 @@
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
     </row>
-    <row r="4" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
+    <row r="4" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
       <c r="J4" s="4"/>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
@@ -1830,436 +1854,424 @@
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
     </row>
-    <row r="5" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="10" t="s">
+    <row r="5" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+    </row>
+    <row r="6" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H6" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I6" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="M5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="4" t="s">
+      <c r="M6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="L7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="M6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="4" t="s">
+      <c r="M7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K8" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="L7" s="5" t="s">
+      <c r="L8" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="M7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="4" t="s">
+      <c r="M8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="L9" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="M8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="4" t="s">
+      <c r="M9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K10" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="L9" s="5" t="s">
+      <c r="L10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="M9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="10" t="s">
+      <c r="M10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="H11" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="I11" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J11" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K11" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="L10" s="5" t="s">
+      <c r="L11" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="M10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="4" t="s">
+      <c r="M11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K12" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="L11" s="5" t="s">
+      <c r="L12" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="M11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="4" t="s">
+      <c r="M12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K13" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="L12" s="5" t="s">
+      <c r="L13" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="M12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N12" s="5" t="s">
+      <c r="M13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N13" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="O12" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-    </row>
-    <row r="14" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="10" t="s">
+      <c r="O13" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+    </row>
+    <row r="15" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="H14" s="13" t="s">
+      <c r="H15" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="I14" s="13" t="s">
+      <c r="I15" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J15" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="K14" s="5" t="s">
+      <c r="K15" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="L14" s="5" t="s">
+      <c r="L15" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="M14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N14" s="5" t="s">
+      <c r="M15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N15" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="O14" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="4" t="s">
+      <c r="O15" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K15" s="5" t="s">
+      <c r="K16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="L15" s="5" t="s">
+      <c r="L16" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="M15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N15" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O15" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="4" t="s">
+      <c r="M16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O16" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="K17" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="L16" s="5" t="s">
+      <c r="L17" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="M16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N16" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O16" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="4" t="s">
+      <c r="M17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O17" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="K17" s="5" t="s">
+      <c r="K18" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="L17" s="5" t="s">
+      <c r="L18" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="M17" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N17" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O17" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="4" t="s">
+      <c r="M18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O18" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="K18" s="5" t="s">
+      <c r="K19" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="L18" s="5" t="s">
+      <c r="L19" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N18" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="O18" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>19</v>
       </c>
       <c r="M19" s="5" t="s">
         <v>14</v>
@@ -2271,82 +2283,82 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
+    <row r="20" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
       <c r="J20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O20" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="K20" s="5" t="s">
+      <c r="K21" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="L20" s="5" t="s">
+      <c r="L21" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="M20" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N20" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O20" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="L21" s="5" t="s">
-        <v>72</v>
-      </c>
       <c r="M21" s="5" t="s">
         <v>14</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O21" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
+    <row r="22" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="10"/>
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
       <c r="J22" s="4" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="M22" s="5" t="s">
         <v>14</v>
@@ -2358,41 +2370,53 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="10" t="s">
+    <row r="23" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N23" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O23" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="10" t="s">
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E24" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F23" s="13" t="s">
+      <c r="F24" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G23" s="10"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-    </row>
-    <row r="24" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
       <c r="J24" s="4"/>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
@@ -2400,16 +2424,16 @@
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
     </row>
-    <row r="25" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
+    <row r="25" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
       <c r="J25" s="4"/>
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
@@ -2417,260 +2441,248 @@
       <c r="N25" s="5"/>
       <c r="O25" s="5"/>
     </row>
-    <row r="26" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="10" t="s">
+    <row r="26" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+    </row>
+    <row r="27" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="H26" s="13" t="s">
+      <c r="H27" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="I26" s="13" t="s">
+      <c r="I27" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="J26" s="4" t="s">
+      <c r="J27" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K26" s="5" t="s">
+      <c r="K27" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="L26" s="5" t="s">
+      <c r="L27" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="M26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N26" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O26" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="4" t="s">
+      <c r="M27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N27" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O27" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K27" s="5" t="s">
+      <c r="K28" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="L27" s="5" t="s">
+      <c r="L28" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="M27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N27" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O27" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="4" t="s">
+      <c r="M28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N28" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O28" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K28" s="5" t="s">
+      <c r="K29" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="L28" s="5" t="s">
+      <c r="L29" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="M28" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N28" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O28" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="11"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="4" t="s">
+      <c r="M29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N29" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O29" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="K29" s="5" t="s">
+      <c r="K30" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="L29" s="5" t="s">
+      <c r="L30" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="M29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N29" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O29" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="4" t="s">
+      <c r="M30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O30" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="K30" s="5" t="s">
+      <c r="K31" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="L30" s="5" t="s">
+      <c r="L31" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="M30" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N30" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O30" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="10" t="s">
+      <c r="M31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N31" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O31" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="13"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="H31" s="13" t="s">
+      <c r="H32" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="I31" s="13" t="s">
+      <c r="I32" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="J31" s="4" t="s">
+      <c r="J32" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="K31" s="5" t="s">
+      <c r="K32" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="L31" s="5" t="s">
+      <c r="L32" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="M31" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N31" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O31" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="4" t="s">
+      <c r="M32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N32" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O32" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="13"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="K32" s="5" t="s">
+      <c r="K33" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="L32" s="5" t="s">
+      <c r="L33" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="M32" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N32" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O32" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="K33" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="L33" s="5" t="s">
-        <v>60</v>
-      </c>
       <c r="M33" s="5" t="s">
         <v>14</v>
       </c>
       <c r="N33" s="5" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O33" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
+    <row r="34" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="13"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
       <c r="J34" s="4" t="s">
         <v>58</v>
       </c>
@@ -2690,30 +2702,24 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H35" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="I35" s="13" t="s">
-        <v>63</v>
-      </c>
+    <row r="35" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="13"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
       <c r="J35" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="L35" s="5" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="M35" s="5" t="s">
         <v>14</v>
@@ -2725,140 +2731,146 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="11"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
+    <row r="36" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="13"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="J36" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L36" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="M36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N36" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O36" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="13"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K36" s="5" t="s">
+      <c r="K37" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="L36" s="5" t="s">
+      <c r="L37" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="M36" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N36" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O36" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="11"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="4" t="s">
+      <c r="M37" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N37" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O37" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="13"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K37" s="5" t="s">
+      <c r="K38" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="L37" s="5" t="s">
+      <c r="L38" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="M37" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N37" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O37" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="11"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="4" t="s">
+      <c r="M38" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N38" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O38" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="13"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="K38" s="5" t="s">
+      <c r="K39" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="L38" s="5" t="s">
+      <c r="L39" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="M38" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N38" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O38" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="11"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="11"/>
-      <c r="J39" s="4" t="s">
+      <c r="M39" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N39" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O39" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="13"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="K39" s="5" t="s">
+      <c r="K40" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="L39" s="5" t="s">
+      <c r="L40" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="M39" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N39" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="O39" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="11"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="11"/>
-      <c r="J40" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K40" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L40" s="5" t="s">
-        <v>19</v>
       </c>
       <c r="M40" s="5" t="s">
         <v>14</v>
@@ -2870,82 +2882,82 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="11"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="12"/>
+    <row r="41" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="13"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
       <c r="J41" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N41" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O41" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="13"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="K41" s="5" t="s">
+      <c r="K42" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="L41" s="5" t="s">
+      <c r="L42" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="M41" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N41" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O41" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="11"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="13"/>
-      <c r="J42" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K42" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="L42" s="5" t="s">
-        <v>72</v>
-      </c>
       <c r="M42" s="5" t="s">
         <v>14</v>
       </c>
       <c r="N42" s="5" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O42" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="12"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
+    <row r="43" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="13"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="10"/>
       <c r="H43" s="12"/>
       <c r="I43" s="12"/>
       <c r="J43" s="4" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="L43" s="5" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="M43" s="5" t="s">
         <v>14</v>
@@ -2957,26 +2969,24 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
+    <row r="44" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="11"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
       <c r="J44" s="4" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L44" s="5" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="M44" s="5" t="s">
         <v>14</v>
@@ -2988,9 +2998,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -3000,16 +3010,28 @@
       <c r="G45" s="4"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="5"/>
-      <c r="L45" s="5"/>
-      <c r="M45" s="5"/>
-      <c r="N45" s="5"/>
-      <c r="O45" s="5"/>
-    </row>
-    <row r="46" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J45" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L45" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M45" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N45" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O45" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -3026,9 +3048,9 @@
       <c r="N46" s="5"/>
       <c r="O46" s="5"/>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -3045,79 +3067,101 @@
       <c r="N47" s="5"/>
       <c r="O47" s="5"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A48" s="7" t="s">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="8"/>
-      <c r="I48" s="8"/>
-      <c r="J48" s="4" t="s">
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="8"/>
+      <c r="I49" s="8"/>
+      <c r="J49" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="K48" s="8"/>
-      <c r="L48" s="8"/>
-      <c r="M48" s="8"/>
-      <c r="N48" s="8"/>
-      <c r="O48" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="8"/>
+      <c r="M49" s="8"/>
+      <c r="N49" s="8"/>
+      <c r="O49" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="A2:A22"/>
-    <mergeCell ref="G10:G12"/>
-    <mergeCell ref="E14:E22"/>
-    <mergeCell ref="I26:I30"/>
-    <mergeCell ref="F2:F13"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="C2:C22"/>
-    <mergeCell ref="F23:F34"/>
-    <mergeCell ref="E2:E13"/>
-    <mergeCell ref="B23:B43"/>
-    <mergeCell ref="H26:H30"/>
-    <mergeCell ref="I42:I43"/>
-    <mergeCell ref="G2:G4"/>
-    <mergeCell ref="H5:H9"/>
-    <mergeCell ref="H14:H20"/>
-    <mergeCell ref="E23:E34"/>
-    <mergeCell ref="H10:H12"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="H31:H33"/>
-    <mergeCell ref="H35:H41"/>
-    <mergeCell ref="D35:D43"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="A23:A43"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="I23:I25"/>
-    <mergeCell ref="F35:F43"/>
-    <mergeCell ref="D23:D34"/>
-    <mergeCell ref="G26:G30"/>
-    <mergeCell ref="G31:G33"/>
-    <mergeCell ref="I31:I33"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="H23:H25"/>
-    <mergeCell ref="G35:G41"/>
-    <mergeCell ref="B2:B22"/>
-    <mergeCell ref="I35:I41"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="D14:D22"/>
-    <mergeCell ref="F14:F22"/>
-    <mergeCell ref="E35:E43"/>
-    <mergeCell ref="G5:G9"/>
-    <mergeCell ref="I5:I9"/>
-    <mergeCell ref="C23:C43"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="I14:I20"/>
-    <mergeCell ref="G14:G20"/>
-    <mergeCell ref="I10:I12"/>
-    <mergeCell ref="D2:D13"/>
+    <mergeCell ref="C24:C44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="I15:I21"/>
+    <mergeCell ref="G15:G21"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="D3:D14"/>
+    <mergeCell ref="D15:D23"/>
+    <mergeCell ref="F15:F23"/>
+    <mergeCell ref="E36:E44"/>
+    <mergeCell ref="G6:G10"/>
+    <mergeCell ref="I6:I10"/>
+    <mergeCell ref="D36:D44"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="A24:A44"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="I24:I26"/>
+    <mergeCell ref="F36:F44"/>
+    <mergeCell ref="D24:D35"/>
+    <mergeCell ref="G27:G31"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="I32:I34"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="H24:H26"/>
+    <mergeCell ref="G36:G42"/>
+    <mergeCell ref="B3:B23"/>
+    <mergeCell ref="I36:I42"/>
+    <mergeCell ref="I3:I5"/>
+    <mergeCell ref="E24:E35"/>
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="H32:H34"/>
+    <mergeCell ref="H36:H42"/>
+    <mergeCell ref="A3:A23"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="E15:E23"/>
+    <mergeCell ref="I27:I31"/>
+    <mergeCell ref="F3:F14"/>
+    <mergeCell ref="H3:H5"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="C3:C23"/>
+    <mergeCell ref="F24:F35"/>
+    <mergeCell ref="E3:E14"/>
+    <mergeCell ref="B24:B44"/>
+    <mergeCell ref="H27:H31"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="H6:H10"/>
+    <mergeCell ref="H15:H21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Mott MacDonald Restricted</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
